--- a/mes_north_sea/clean_data/new_technologies/NewTechnologies.xlsx
+++ b/mes_north_sea/clean_data/new_technologies/NewTechnologies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\6574114\Documents\Research\EHUB-Py_Productive\mes_north_sea\clean_data\new_technologies\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maiant/PycharmProjects/Key-Infrastructure-North-Sea-CodeAndData/mes_north_sea/clean_data/new_technologies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF7B7513-1D76-4972-A59B-0DBB7DD14347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC41C41-764F-6842-AA57-FA80F64574EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
   </bookViews>
   <sheets>
     <sheet name="NewTechnologies" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="76">
   <si>
     <t>Electrolyser_PEM_offshore</t>
   </si>
@@ -262,6 +262,12 @@
   </si>
   <si>
     <t>Storage_Battery_new_HP</t>
+  </si>
+  <si>
+    <t>PermanentStorage_CO2_simple</t>
+  </si>
+  <si>
+    <t>DAC_Adsorption_onshore</t>
   </si>
 </sst>
 </file>
@@ -586,19 +592,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="15.33203125" customWidth="1"/>
     <col min="12" max="12" width="43" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="34" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="43" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -651,13 +657,16 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
+      <c r="C2" t="s">
+        <v>74</v>
+      </c>
       <c r="E2" t="s">
         <v>54</v>
       </c>
@@ -680,13 +689,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>21</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
       <c r="E3" t="s">
         <v>54</v>
       </c>
@@ -709,13 +721,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
+      <c r="C4" t="s">
+        <v>74</v>
+      </c>
       <c r="E4" t="s">
         <v>54</v>
       </c>
@@ -738,13 +753,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
       <c r="E5" t="s">
         <v>54</v>
       </c>
@@ -767,13 +785,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
       </c>
+      <c r="C6" t="s">
+        <v>74</v>
+      </c>
       <c r="E6" t="s">
         <v>54</v>
       </c>
@@ -796,13 +817,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>30</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
+      <c r="C7" t="s">
+        <v>74</v>
+      </c>
       <c r="E7" t="s">
         <v>54</v>
       </c>
@@ -825,13 +849,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>34</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
       </c>
+      <c r="C8" t="s">
+        <v>74</v>
+      </c>
       <c r="E8" t="s">
         <v>54</v>
       </c>
@@ -854,13 +881,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>35</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
       </c>
+      <c r="C9" t="s">
+        <v>74</v>
+      </c>
       <c r="E9" t="s">
         <v>54</v>
       </c>
@@ -883,13 +913,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>36</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
       </c>
+      <c r="C10" t="s">
+        <v>74</v>
+      </c>
       <c r="E10" t="s">
         <v>54</v>
       </c>
@@ -912,13 +945,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>46</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
       </c>
+      <c r="C11" t="s">
+        <v>74</v>
+      </c>
       <c r="E11" t="s">
         <v>54</v>
       </c>
@@ -941,13 +977,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>47</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
       </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
       <c r="E12" t="s">
         <v>54</v>
       </c>
@@ -970,13 +1009,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>48</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
       </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
       <c r="E13" t="s">
         <v>54</v>
       </c>
@@ -999,13 +1041,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
       </c>
+      <c r="C14" t="s">
+        <v>74</v>
+      </c>
       <c r="E14" t="s">
         <v>54</v>
       </c>
@@ -1028,13 +1073,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>19</v>
       </c>
       <c r="B15" t="s">
         <v>7</v>
       </c>
+      <c r="C15" t="s">
+        <v>74</v>
+      </c>
       <c r="E15" t="s">
         <v>54</v>
       </c>
@@ -1057,13 +1105,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>20</v>
       </c>
       <c r="B16" t="s">
         <v>7</v>
       </c>
+      <c r="C16" t="s">
+        <v>74</v>
+      </c>
       <c r="E16" t="s">
         <v>54</v>
       </c>
@@ -1086,13 +1137,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>29</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
       </c>
+      <c r="C17" t="s">
+        <v>74</v>
+      </c>
       <c r="E17" t="s">
         <v>54</v>
       </c>
@@ -1115,13 +1169,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>32</v>
       </c>
       <c r="B18" t="s">
         <v>7</v>
       </c>
+      <c r="C18" t="s">
+        <v>74</v>
+      </c>
       <c r="E18" t="s">
         <v>54</v>
       </c>
@@ -1144,13 +1201,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>33</v>
       </c>
       <c r="B19" t="s">
         <v>7</v>
       </c>
+      <c r="C19" t="s">
+        <v>74</v>
+      </c>
       <c r="E19" t="s">
         <v>54</v>
       </c>
@@ -1173,13 +1233,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>42</v>
       </c>
       <c r="B20" t="s">
         <v>7</v>
       </c>
+      <c r="C20" t="s">
+        <v>74</v>
+      </c>
       <c r="E20" t="s">
         <v>54</v>
       </c>
@@ -1202,13 +1265,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>43</v>
       </c>
       <c r="B21" t="s">
         <v>7</v>
       </c>
+      <c r="C21" t="s">
+        <v>74</v>
+      </c>
       <c r="E21" t="s">
         <v>54</v>
       </c>
@@ -1231,13 +1297,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>44</v>
       </c>
       <c r="B22" t="s">
         <v>7</v>
       </c>
+      <c r="C22" t="s">
+        <v>74</v>
+      </c>
       <c r="E22" t="s">
         <v>54</v>
       </c>
@@ -1260,13 +1329,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>45</v>
       </c>
       <c r="B23" t="s">
         <v>7</v>
       </c>
+      <c r="C23" t="s">
+        <v>74</v>
+      </c>
       <c r="E23" t="s">
         <v>54</v>
       </c>
@@ -1289,13 +1361,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>17</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
       </c>
+      <c r="C24" t="s">
+        <v>75</v>
+      </c>
       <c r="D24" t="s">
         <v>53</v>
       </c>
@@ -1324,13 +1399,16 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>18</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
+      <c r="C25" t="s">
+        <v>75</v>
+      </c>
       <c r="D25" t="s">
         <v>53</v>
       </c>
@@ -1359,13 +1437,16 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>25</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
+      <c r="C26" t="s">
+        <v>75</v>
+      </c>
       <c r="D26" t="s">
         <v>53</v>
       </c>
@@ -1394,13 +1475,16 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>26</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
       </c>
+      <c r="C27" t="s">
+        <v>75</v>
+      </c>
       <c r="D27" t="s">
         <v>53</v>
       </c>
@@ -1429,13 +1513,16 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>27</v>
       </c>
       <c r="B28" t="s">
         <v>9</v>
       </c>
+      <c r="C28" t="s">
+        <v>75</v>
+      </c>
       <c r="D28" t="s">
         <v>53</v>
       </c>
@@ -1464,13 +1551,16 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>28</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
       </c>
+      <c r="C29" t="s">
+        <v>75</v>
+      </c>
       <c r="D29" t="s">
         <v>53</v>
       </c>
@@ -1499,13 +1589,16 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>31</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
       </c>
+      <c r="C30" t="s">
+        <v>75</v>
+      </c>
       <c r="D30" t="s">
         <v>53</v>
       </c>
@@ -1534,13 +1627,16 @@
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>37</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
       </c>
+      <c r="C31" t="s">
+        <v>75</v>
+      </c>
       <c r="D31" t="s">
         <v>53</v>
       </c>
@@ -1569,13 +1665,16 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>38</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
       </c>
+      <c r="C32" t="s">
+        <v>75</v>
+      </c>
       <c r="D32" t="s">
         <v>53</v>
       </c>
@@ -1604,13 +1703,16 @@
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>39</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
       </c>
+      <c r="C33" t="s">
+        <v>75</v>
+      </c>
       <c r="D33" t="s">
         <v>53</v>
       </c>
@@ -1639,13 +1741,16 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>40</v>
       </c>
       <c r="B34" t="s">
         <v>9</v>
       </c>
+      <c r="C34" t="s">
+        <v>75</v>
+      </c>
       <c r="D34" t="s">
         <v>53</v>
       </c>
@@ -1674,13 +1779,16 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>41</v>
       </c>
       <c r="B35" t="s">
         <v>9</v>
       </c>
+      <c r="C35" t="s">
+        <v>75</v>
+      </c>
       <c r="D35" t="s">
         <v>53</v>
       </c>
@@ -1709,13 +1817,16 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>49</v>
       </c>
       <c r="B36" t="s">
         <v>9</v>
       </c>
+      <c r="C36" t="s">
+        <v>75</v>
+      </c>
       <c r="D36" t="s">
         <v>53</v>
       </c>
@@ -1744,13 +1855,16 @@
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>50</v>
       </c>
       <c r="B37" t="s">
         <v>9</v>
       </c>
+      <c r="C37" t="s">
+        <v>75</v>
+      </c>
       <c r="D37" t="s">
         <v>53</v>
       </c>
@@ -1779,13 +1893,16 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>51</v>
       </c>
       <c r="B38" t="s">
         <v>9</v>
       </c>
+      <c r="C38" t="s">
+        <v>75</v>
+      </c>
       <c r="D38" t="s">
         <v>53</v>
       </c>
@@ -1814,12 +1931,15 @@
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>52</v>
       </c>
       <c r="B39" t="s">
         <v>9</v>
+      </c>
+      <c r="C39" t="s">
+        <v>75</v>
       </c>
       <c r="D39" t="s">
         <v>53</v>
@@ -1864,15 +1984,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33D5EF00-EA79-4AEB-B3C3-D33E39C14C3D}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>1</v>
       </c>
@@ -1883,7 +2003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1894,7 +2014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1905,7 +2025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>

--- a/mes_north_sea/clean_data/new_technologies/NewTechnologies.xlsx
+++ b/mes_north_sea/clean_data/new_technologies/NewTechnologies.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC41C41-764F-6842-AA57-FA80F64574EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
   </bookViews>
   <sheets>
     <sheet name="NewTechnologies" sheetId="1" r:id="rId1"/>
